--- a/data/trans_orig/IP42B-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP42B-Provincia-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2750</t>
+          <t>2833</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>4012</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5241</t>
+          <t>5417</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,76%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6972</t>
+          <t>6889</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12440</t>
+          <t>12353</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20846</t>
+          <t>20670</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>658</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5206</t>
+          <t>5711</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>3398</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7130</t>
+          <t>7024</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,57%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11291</t>
+          <t>10786</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15867</t>
+          <t>15839</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18025</t>
+          <t>17928</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>30693</t>
+          <t>30799</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>36562</t>
+          <t>36552</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4892</t>
+          <t>4937</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4711</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11284</t>
+          <t>11239</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35802</t>
+          <t>36212</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>651</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5598</t>
+          <t>5432</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>3449</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>859</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6797</t>
+          <t>7213</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,96%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9172</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13932</t>
+          <t>13953</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14313</t>
+          <t>14800</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>26057</t>
+          <t>25641</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>31560</t>
+          <t>31995</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2578</t>
+          <t>2647</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,6%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>683</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>5675</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>629</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5431</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>641</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>5774</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>14,46%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15246</t>
+          <t>15610</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20034</t>
+          <t>20048</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>35059</t>
+          <t>34164</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>39303</t>
+          <t>39297</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,39%</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4122</t>
+          <t>4601</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7777</t>
+          <t>7717</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2653</t>
+          <t>2663</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9675</t>
+          <t>10182</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>17,03%</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>26829</t>
+          <t>26350</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>21068</t>
+          <t>21128</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>27462</t>
+          <t>27445</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>50121</t>
+          <t>49614</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>57143</t>
+          <t>57133</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,55%</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4398</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2724</t>
+          <t>2739</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9608</t>
+          <t>9484</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>4127</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11691</t>
+          <t>12068</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>23,42%</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>19681</t>
+          <t>19814</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>17838</t>
+          <t>17962</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24722</t>
+          <t>24707</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>39833</t>
+          <t>39456</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>47914</t>
+          <t>47397</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>91,99%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7944</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>18744</t>
+          <t>18363</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6922</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17956</t>
+          <t>17396</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>16854</t>
+          <t>17329</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>32322</t>
+          <t>33111</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>117293</t>
+          <t>117674</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>128435</t>
+          <t>128093</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>142839</t>
+          <t>143399</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>153873</t>
+          <t>153950</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>264510</t>
+          <t>263721</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>279978</t>
+          <t>279503</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,16%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>1079</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2665</t>
+          <t>2773</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9037</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5134</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12832</t>
+          <t>13057</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>49,42%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>6812</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11691</t>
+          <t>11745</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4559</t>
+          <t>4635</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10931</t>
+          <t>10823</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13588</t>
+          <t>13363</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21286</t>
+          <t>21279</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,54%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2574</t>
+          <t>2538</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9130</t>
+          <t>9173</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2427</t>
+          <t>2579</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9138</t>
+          <t>9484</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6487</t>
+          <t>6417</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15749</t>
+          <t>15588</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,75%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24491</t>
+          <t>24448</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31047</t>
+          <t>31083</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>25773</t>
+          <t>25427</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32484</t>
+          <t>32332</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>52783</t>
+          <t>52944</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>62045</t>
+          <t>62115</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,64%</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3401</t>
+          <t>3619</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4345</t>
+          <t>4352</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>641</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,16%</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12753</t>
+          <t>12535</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10471</t>
+          <t>10464</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26005</t>
+          <t>25966</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30314</t>
+          <t>30330</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8294</t>
+          <t>8357</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3547</t>
+          <t>2817</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2554</t>
+          <t>2540</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10024</t>
+          <t>9567</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>24,93%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10435</t>
+          <t>10372</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16703</t>
+          <t>16741</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16106</t>
+          <t>16836</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28358</t>
+          <t>28815</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>35828</t>
+          <t>35842</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,38%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>714</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6056</t>
+          <t>5866</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3140</t>
+          <t>3139</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1528</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7780</t>
+          <t>7439</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>41,0%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3797</t>
+          <t>3987</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8848</t>
+          <t>9139</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10363</t>
+          <t>10704</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16615</t>
+          <t>16633</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,68%</t>
         </is>
       </c>
     </row>
@@ -5775,7 +5775,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4165</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>455</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4431</t>
+          <t>4587</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6290</t>
+          <t>6977</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>26,52%</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6199</t>
+          <t>6785</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>65,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11511</t>
+          <t>11355</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15488</t>
+          <t>15487</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20016</t>
+          <t>19329</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>25173</t>
+          <t>25165</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4340</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12953</t>
+          <t>12935</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4570</t>
+          <t>4640</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12773</t>
+          <t>12889</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11019</t>
+          <t>11134</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23255</t>
+          <t>23312</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,04%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>27357</t>
+          <t>27375</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>35970</t>
+          <t>36008</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24515</t>
+          <t>24399</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>32718</t>
+          <t>32648</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>54343</t>
+          <t>54286</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>66579</t>
+          <t>66464</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>69,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,65%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>590</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5179</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>684</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6075</t>
+          <t>6473</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2157</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9519</t>
+          <t>9140</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>31672</t>
+          <t>31798</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>36249</t>
+          <t>36261</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>37463</t>
+          <t>37065</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>42814</t>
+          <t>42854</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>70871</t>
+          <t>71250</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>78233</t>
+          <t>78329</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,44%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>20048</t>
+          <t>21221</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>36695</t>
+          <t>37511</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>19076</t>
+          <t>19449</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>35275</t>
+          <t>35299</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>44175</t>
+          <t>43786</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>66638</t>
+          <t>66645</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>142012</t>
+          <t>141196</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>158659</t>
+          <t>157486</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>152759</t>
+          <t>152735</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>168958</t>
+          <t>168585</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>300103</t>
+          <t>300096</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>322566</t>
+          <t>322955</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>88,06%</t>
         </is>
       </c>
     </row>
@@ -7378,12 +7378,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>446</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4585</t>
+          <t>4452</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>639</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6412</t>
+          <t>6161</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2176</t>
+          <t>2164</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8572</t>
+          <t>8647</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,2%</t>
         </is>
       </c>
     </row>
@@ -7491,12 +7491,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12920</t>
+          <t>13053</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17030</t>
+          <t>17059</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13351</t>
+          <t>13602</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19111</t>
+          <t>19124</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28696</t>
+          <t>28621</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35092</t>
+          <t>35104</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,19%</t>
         </is>
       </c>
     </row>
@@ -7721,12 +7721,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8442</t>
+          <t>8385</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1356</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7047</t>
+          <t>7621</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3968</t>
+          <t>4606</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13057</t>
+          <t>12969</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,89%</t>
         </is>
       </c>
     </row>
@@ -7834,12 +7834,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25392</t>
+          <t>25449</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31953</t>
+          <t>31964</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>35884</t>
+          <t>35310</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>41575</t>
+          <t>41592</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>63708</t>
+          <t>63796</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>72797</t>
+          <t>72159</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,0%</t>
         </is>
       </c>
     </row>
@@ -8069,7 +8069,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>4128</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>3284</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8119,7 +8119,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8139,7 +8139,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>4348</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -8177,7 +8177,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14580</t>
+          <t>14071</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8192,7 +8192,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21460</t>
+          <t>21477</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -8227,7 +8227,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8247,7 +8247,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>37870</t>
+          <t>38612</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8412,7 +8412,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1452</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8213</t>
+          <t>8436</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8457,12 +8457,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>2219</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9843</t>
+          <t>9981</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,21%</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20601</t>
+          <t>20357</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21518</t>
+          <t>21295</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28279</t>
+          <t>28276</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8570,12 +8570,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>44960</t>
+          <t>44822</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>52481</t>
+          <t>52584</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,95%</t>
         </is>
       </c>
     </row>
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3556</t>
+          <t>3590</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4082</t>
+          <t>3345</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8805,7 +8805,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4067</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -8863,7 +8863,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12125</t>
+          <t>12091</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17930</t>
+          <t>18667</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8933,7 +8933,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>33626</t>
+          <t>32992</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9098,7 +9098,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3156</t>
+          <t>3144</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4578</t>
+          <t>4632</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>610</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5711</t>
+          <t>5739</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>9137</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6258</t>
+          <t>6204</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>17406</t>
+          <t>17378</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>22512</t>
+          <t>22507</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,36%</t>
         </is>
       </c>
     </row>
@@ -9436,12 +9436,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7299</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>584</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>5007</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2555</t>
+          <t>2515</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9788</t>
+          <t>9899</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -9549,12 +9549,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>26306</t>
+          <t>26499</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>32313</t>
+          <t>32298</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9584,12 +9584,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>39124</t>
+          <t>39083</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>44090</t>
+          <t>43506</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9599,12 +9599,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>67907</t>
+          <t>67796</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>75140</t>
+          <t>75180</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,76%</t>
         </is>
       </c>
     </row>
@@ -9779,12 +9779,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8409</t>
+          <t>8368</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>656</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6568</t>
+          <t>6233</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3306</t>
+          <t>3465</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11042</t>
+          <t>11439</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -9892,12 +9892,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>37488</t>
+          <t>37529</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>44353</t>
+          <t>44378</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9907,12 +9907,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>33843</t>
+          <t>34178</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>39673</t>
+          <t>39755</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>75266</t>
+          <t>74869</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>83002</t>
+          <t>82843</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>95,99%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>11426</t>
+          <t>12180</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>24573</t>
+          <t>24540</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>11986</t>
+          <t>11510</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>24817</t>
+          <t>25294</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,12 +10172,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>26344</t>
+          <t>26230</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>45078</t>
+          <t>45458</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>177500</t>
+          <t>177533</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>190647</t>
+          <t>189893</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>209718</t>
+          <t>209241</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>222549</t>
+          <t>223025</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>391530</t>
+          <t>391150</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>410264</t>
+          <t>410378</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,99%</t>
         </is>
       </c>
     </row>
